--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.37638775810591</v>
+        <v>8.673663010692209</v>
       </c>
       <c r="D2" t="n">
-        <v>52.81225194007376</v>
+        <v>8.581990940261987</v>
       </c>
       <c r="E2" t="n">
-        <v>20.36064371607868</v>
+        <v>3.308604603862786</v>
       </c>
       <c r="F2" t="n">
-        <v>16.27122257329668</v>
+        <v>2.644073668160711</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.343065952932509</v>
+        <v>1.355748217351533</v>
       </c>
       <c r="D3" t="n">
-        <v>7.487910764062587</v>
+        <v>1.21678549916017</v>
       </c>
       <c r="E3" t="n">
-        <v>20.36064371607868</v>
+        <v>3.308604603862786</v>
       </c>
       <c r="F3" t="n">
-        <v>16.27122257329668</v>
+        <v>2.644073668160711</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.562796947235563</v>
+        <v>1.391454503925779</v>
       </c>
       <c r="D4" t="n">
-        <v>17.89914206586733</v>
+        <v>2.908610585703441</v>
       </c>
       <c r="E4" t="n">
-        <v>20.36064371607868</v>
+        <v>3.308604603862786</v>
       </c>
       <c r="F4" t="n">
-        <v>16.27122257329668</v>
+        <v>2.644073668160711</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.55973397514501</v>
+        <v>8.215956770961064</v>
       </c>
       <c r="D5" t="n">
-        <v>1.564458648925413</v>
+        <v>0.2542245304503797</v>
       </c>
       <c r="E5" t="n">
-        <v>20.36064371607868</v>
+        <v>3.308604603862786</v>
       </c>
       <c r="F5" t="n">
-        <v>16.27122257329668</v>
+        <v>2.644073668160711</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.28690922700102</v>
+        <v>5.246622749387666</v>
       </c>
       <c r="D6" t="n">
-        <v>23.52959785692569</v>
+        <v>3.823559651750424</v>
       </c>
       <c r="E6" t="n">
-        <v>20.36064371607868</v>
+        <v>3.308604603862786</v>
       </c>
       <c r="F6" t="n">
-        <v>16.27122257329668</v>
+        <v>2.644073668160711</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.100433519964723</v>
+        <v>0.6663204469942676</v>
       </c>
       <c r="D7" t="n">
-        <v>19.71109928041177</v>
+        <v>3.203053633066913</v>
       </c>
       <c r="E7" t="n">
-        <v>20.36064371607868</v>
+        <v>3.308604603862786</v>
       </c>
       <c r="F7" t="n">
-        <v>16.27122257329668</v>
+        <v>2.644073668160711</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
